--- a/reports/shareable_20261005/technical/TECHNICAL_REVIEW.xlsx
+++ b/reports/shareable_20261005/technical/TECHNICAL_REVIEW.xlsx
@@ -10,13 +10,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claims" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funding quotes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release decisions" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parts register" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pressure screening" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pressure assumptions" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fasteners" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Display dimensions" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Room scenarios" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funding quotes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release decisions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parts register" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pressure screening" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pressure assumptions" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fasteners" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Display dimensions" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read me'!$A$1:$B$6</definedName>
@@ -25,20 +26,22 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Milestones'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Claims'!$A$1:$C$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Claims'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Funding quotes'!$A$1:$M$16</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Funding quotes'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Release decisions'!$A$1:$J$13</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Release decisions'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Parts register'!$A$1:$F$16</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Parts register'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Pressure screening'!$A$1:$K$16</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Pressure screening'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Pressure assumptions'!$A$1:$B$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Pressure assumptions'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Fasteners'!$A$1:$D$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Fasteners'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Display dimensions'!$A$1:$F$494</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Display dimensions'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Room scenarios'!$A$1:$H$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Room scenarios'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Funding quotes'!$A$1:$M$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Funding quotes'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Release decisions'!$A$1:$J$13</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Release decisions'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Parts register'!$A$1:$F$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Parts register'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Pressure screening'!$A$1:$K$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Pressure screening'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Pressure assumptions'!$A$1:$B$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Pressure assumptions'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Fasteners'!$A$1:$D$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Fasteners'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Display dimensions'!$A$1:$F$494</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Display dimensions'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -90,13 +93,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -556,6 +565,226 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18.2" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="45.5" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>qty</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>spec</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>M5 reducer studs</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>12 x60 mm;4 x40 mm;32 nuts8AFx5;32 washers15ODx1.2 (bore5.3 assumed)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>PROPOSED; external thread projection2.8mm; inner3.8mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Seal compression limiters</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>16 outer OD10/ID5.5 x3;8 inner OD6.5/ID4.5 x36</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>ASSUMED nominal gaps; force/tolerance/actual filter thickness unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Fan fastenings</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>M4x50 cap screw;32 washers12ODx1;16 nuts7AFx5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>PROPOSED;6mm nominal thread projection; fan corner bearing strength unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Cabinet through joints</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>M4x40 cap screws;64 washers12ODx1;32 nuts7AFx5</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSED;4mm nominal thread projection; wood bearing/edge and clamp load not approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Top/base wood screws</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>4 top4x20;4 base4x25;8 washers;head7dia x4 envelope</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Core only; thread/pilot, wood grade and end-grain withdrawal must be verified; never lift by lid</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Foot retention</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>M4x30 cap screw;8 washers12ODx1;4 nuts7AFx5;4 feet with12dia x9 recess</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSED; head4mm above floor;3mm nominal thread projection; foot material strength unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Retained adapter M4 hardware</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>8 M4x80 studs;4 M4x25 ledge screws;28 nuts;32 washers</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>R02H geometry retained; sealing washers separate</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="38" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Independent guard bolts</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>8 M4x20 screws;8 nuts;16 washers</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>R02G mounting stacks retained; welded cage replaces rivets</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -13702,6 +13931,216 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14.95" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="25.35" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ASSUMED area m2</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ASSUMED height m</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ASSUMED CADR m3/h</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Target fraction reduced</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Volume m3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ideal target minutes</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Required CADR for30 min</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="68" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E2" s="2">
+        <f>IF(AND(ISNUMBER(A2),A2&gt;0,ISNUMBER(B2),B2&gt;0,ISNUMBER(C2),C2&gt;=0,ISNUMBER(D2),D2&gt;0,D2&lt;1),A2*B2,"INVALID INPUT")</f>
+        <v/>
+      </c>
+      <c r="F2" s="2">
+        <f>IF(AND(ISNUMBER(A2),A2&gt;0,ISNUMBER(B2),B2&gt;0,ISNUMBER(C2),C2&gt;=0,ISNUMBER(D2),D2&gt;0,D2&lt;1),IF(C2&gt;0,-60*E2*LN(1-D2)/C2,"NO MODELED CLEANING"),"INVALID INPUT")</f>
+        <v/>
+      </c>
+      <c r="G2" s="2">
+        <f>IF(AND(ISNUMBER(A2),A2&gt;0,ISNUMBER(B2),B2&gt;0,ISNUMBER(C2),C2&gt;=0,ISNUMBER(D2),D2&gt;0,D2&lt;1),-2*E2*LN(1-D2),"INVALID INPUT")</f>
+        <v/>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Illustrative only; no measured D01 CADR</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="68" customHeight="1">
+      <c r="A3" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E3" s="3">
+        <f>IF(AND(ISNUMBER(A3),A3&gt;0,ISNUMBER(B3),B3&gt;0,ISNUMBER(C3),C3&gt;=0,ISNUMBER(D3),D3&gt;0,D3&lt;1),A3*B3,"INVALID INPUT")</f>
+        <v/>
+      </c>
+      <c r="F3" s="3">
+        <f>IF(AND(ISNUMBER(A3),A3&gt;0,ISNUMBER(B3),B3&gt;0,ISNUMBER(C3),C3&gt;=0,ISNUMBER(D3),D3&gt;0,D3&lt;1),IF(C3&gt;0,-60*E3*LN(1-D3)/C3,"NO MODELED CLEANING"),"INVALID INPUT")</f>
+        <v/>
+      </c>
+      <c r="G3" s="3">
+        <f>IF(AND(ISNUMBER(A3),A3&gt;0,ISNUMBER(B3),B3&gt;0,ISNUMBER(C3),C3&gt;=0,ISNUMBER(D3),D3&gt;0,D3&lt;1),-2*E3*LN(1-D3),"INVALID INPUT")</f>
+        <v/>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Illustrative only; no measured D01 CADR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="68" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E4" s="2">
+        <f>IF(AND(ISNUMBER(A4),A4&gt;0,ISNUMBER(B4),B4&gt;0,ISNUMBER(C4),C4&gt;=0,ISNUMBER(D4),D4&gt;0,D4&lt;1),A4*B4,"INVALID INPUT")</f>
+        <v/>
+      </c>
+      <c r="F4" s="2">
+        <f>IF(AND(ISNUMBER(A4),A4&gt;0,ISNUMBER(B4),B4&gt;0,ISNUMBER(C4),C4&gt;=0,ISNUMBER(D4),D4&gt;0,D4&lt;1),IF(C4&gt;0,-60*E4*LN(1-D4)/C4,"NO MODELED CLEANING"),"INVALID INPUT")</f>
+        <v/>
+      </c>
+      <c r="G4" s="2">
+        <f>IF(AND(ISNUMBER(A4),A4&gt;0,ISNUMBER(B4),B4&gt;0,ISNUMBER(C4),C4&gt;=0,ISNUMBER(D4),D4&gt;0,D4&lt;1),-2*E4*LN(1-D4),"INVALID INPUT")</f>
+        <v/>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Illustrative only; no measured D01 CADR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="68" customHeight="1">
+      <c r="A5" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E5" s="3">
+        <f>IF(AND(ISNUMBER(A5),A5&gt;0,ISNUMBER(B5),B5&gt;0,ISNUMBER(C5),C5&gt;=0,ISNUMBER(D5),D5&gt;0,D5&lt;1),A5*B5,"INVALID INPUT")</f>
+        <v/>
+      </c>
+      <c r="F5" s="3">
+        <f>IF(AND(ISNUMBER(A5),A5&gt;0,ISNUMBER(B5),B5&gt;0,ISNUMBER(C5),C5&gt;=0,ISNUMBER(D5),D5&gt;0,D5&lt;1),IF(C5&gt;0,-60*E5*LN(1-D5)/C5,"NO MODELED CLEANING"),"INVALID INPUT")</f>
+        <v/>
+      </c>
+      <c r="G5" s="3">
+        <f>IF(AND(ISNUMBER(A5),A5&gt;0,ISNUMBER(B5),B5&gt;0,ISNUMBER(C5),C5&gt;=0,ISNUMBER(D5),D5&gt;0,D5&lt;1),-2*E5*LN(1-D5),"INVALID INPUT")</f>
+        <v/>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Illustrative only; no measured D01 CADR</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H5"/>
+  <dataValidations count="4">
+    <dataValidation sqref="A2:A5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid scenario" error="Use a positive area/height, nonnegative CADR, and a reduction fraction strictly between0 and1." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0.1</formula1>
+      <formula2>10000</formula2>
+    </dataValidation>
+    <dataValidation sqref="B2:B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid scenario" error="Use a positive area/height, nonnegative CADR, and a reduction fraction strictly between0 and1." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0.1</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation sqref="C2:C5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid scenario" error="Use a positive area/height, nonnegative CADR, and a reduction fraction strictly between0 and1." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>100000</formula2>
+    </dataValidation>
+    <dataValidation sqref="D2:D5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid scenario" error="Use a positive area/height, nonnegative CADR, and a reduction fraction strictly between0 and1." type="decimal" errorStyle="stop" operator="between">
+      <formula1>1e-06</formula1>
+      <formula2>0.999999</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14297,7 +14736,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14857,7 +15296,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15393,7 +15832,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16004,7 +16443,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16070,224 +16509,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18.2" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="45.5" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>item</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>qty</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>spec</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="38" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>M5 reducer studs</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>12 x60 mm;4 x40 mm;32 nuts8AFx5;32 washers15ODx1.2 (bore5.3 assumed)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>PROPOSED; external thread projection2.8mm; inner3.8mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Seal compression limiters</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>16 outer OD10/ID5.5 x3;8 inner OD6.5/ID4.5 x36</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>ASSUMED nominal gaps; force/tolerance/actual filter thickness unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Fan fastenings</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>M4x50 cap screw;32 washers12ODx1;16 nuts7AFx5</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>PROPOSED;6mm nominal thread projection; fan corner bearing strength unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Cabinet through joints</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>M4x40 cap screws;64 washers12ODx1;32 nuts7AFx5</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED;4mm nominal thread projection; wood bearing/edge and clamp load not approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Top/base wood screws</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4 top4x20;4 base4x25;8 washers;head7dia x4 envelope</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Core only; thread/pilot, wood grade and end-grain withdrawal must be verified; never lift by lid</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Foot retention</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>M4x30 cap screw;8 washers12ODx1;4 nuts7AFx5;4 feet with12dia x9 recess</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED; head4mm above floor;3mm nominal thread projection; foot material strength unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Retained adapter M4 hardware</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>8 M4x80 studs;4 M4x25 ledge screws;28 nuts;32 washers</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>R02H geometry retained; sealing washers separate</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="38" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Independent guard bolts</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>8 M4x20 screws;8 nuts;16 washers</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>R02G mounting stacks retained; welded cage replaces rivets</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:D9"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/reports/shareable_20261005/technical/TECHNICAL_REVIEW.xlsx
+++ b/reports/shareable_20261005/technical/TECHNICAL_REVIEW.xlsx
@@ -12,12 +12,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claims" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Room scenarios" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funding quotes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release decisions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parts register" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pressure screening" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pressure assumptions" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fasteners" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Display dimensions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Current release gates" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control module placement" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release decisions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parts register" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pressure screening" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pressure assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fasteners" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Display dimensions" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read me'!$A$1:$B$6</definedName>
@@ -30,18 +32,22 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Room scenarios'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Funding quotes'!$A$1:$M$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Funding quotes'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Release decisions'!$A$1:$J$13</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Release decisions'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Parts register'!$A$1:$F$16</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Parts register'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Pressure screening'!$A$1:$K$16</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Pressure screening'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Pressure assumptions'!$A$1:$B$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Pressure assumptions'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Fasteners'!$A$1:$D$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Fasteners'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Display dimensions'!$A$1:$F$494</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Display dimensions'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Current release gates'!$A$1:$J$14</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Current release gates'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Control module placement'!$A$1:$H$19</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Control module placement'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Release decisions'!$A$1:$J$13</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Release decisions'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Parts register'!$A$1:$F$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Parts register'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Pressure screening'!$A$1:$K$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Pressure screening'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Pressure assumptions'!$A$1:$B$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Pressure assumptions'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Fasteners'!$A$1:$D$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'Fasteners'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Display dimensions'!$A$1:$F$494</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'Display dimensions'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -565,6 +571,685 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>total_m3h</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>per_filter_m3h</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>reducer_K</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>fan_Pa</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>plenum_Pa</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>inner_guard_Pa</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>outer_guard_Pa</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>installation_Pa</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>reducer_Pa</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>nonfilter_Pa</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>filter_allowance_Pa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>32.59998230680289</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.8677361498395474</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>2.208837426402051</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>2.208837426402051</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0.5784907665596982</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0.02592105276800554</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>5.889822821971354</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>26.71015948483153</v>
+      </c>
+    </row>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>32.59998230680289</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0.8677361498395474</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>2.208837426402051</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>2.208837426402051</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0.5784907665596982</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0.05184210553601108</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>5.915743874739359</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>26.68423843206353</v>
+      </c>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>32.59998230680289</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.8677361498395474</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>2.208837426402051</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>2.208837426402051</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.5784907665596982</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0.1036842110720222</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>5.967585980275371</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>26.63239632652752</v>
+      </c>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>30.09391027851171</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1.355837734124293</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>3.451308478753206</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>3.451308478753206</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0.9038918227495287</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0.04050164495000866</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>9.202848159330243</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>20.89106211918147</v>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>30.09391027851171</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>1.355837734124293</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>3.451308478753206</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>3.451308478753206</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.9038918227495287</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0.08100328990001732</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>9.243349804280252</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>20.85056047423146</v>
+      </c>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>30.09391027851171</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1.355837734124293</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>3.451308478753206</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>3.451308478753206</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0.9038918227495287</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0.1620065798000346</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>9.324353094180269</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>20.76955718433144</v>
+      </c>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>27.62649553528014</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>1.952406337138982</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>4.969884209404615</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>4.969884209404615</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>1.301604224759321</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.05832236872801246</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>13.25210134943555</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>14.3743941858446</v>
+      </c>
+    </row>
+    <row r="9" ht="38" customHeight="1">
+      <c r="A9" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>27.62649553528014</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1.952406337138982</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>4.969884209404615</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>4.969884209404615</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>1.301604224759321</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>0.1166447374560249</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>13.31042371816356</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>14.31607181711659</v>
+      </c>
+    </row>
+    <row r="10" ht="38" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>27.62649553528014</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>1.952406337138982</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>4.969884209404615</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>4.969884209404615</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>1.301604224759321</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0.2332894749120498</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>13.42706845561958</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>14.19942707966056</v>
+      </c>
+    </row>
+    <row r="11" ht="38" customHeight="1">
+      <c r="A11" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>25.26773196530823</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>2.657441958883614</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>6.764564618356284</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>6.764564618356284</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>1.771627972589076</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>0.07938322410201697</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>18.03758239228728</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>7.230149573020956</v>
+      </c>
+    </row>
+    <row r="12" ht="38" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>25.26773196530823</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>2.657441958883614</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>6.764564618356284</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>6.764564618356284</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>1.771627972589076</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0.1587664482040339</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>18.11696561638929</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>7.150766348918939</v>
+      </c>
+    </row>
+    <row r="13" ht="38" customHeight="1">
+      <c r="A13" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>25.26773196530823</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>2.657441958883614</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>6.764564618356284</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>6.764564618356284</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>1.771627972589076</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>0.3175328964080679</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>18.27573206459333</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>6.991999900714905</v>
+      </c>
+    </row>
+    <row r="14" ht="38" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>22.83386008460588</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>3.47094459935819</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>8.835349705608206</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>8.835349705608206</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>2.313963066238793</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0.1036842110720222</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>23.55929128788542</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>-0.7254312032795305</v>
+      </c>
+    </row>
+    <row r="15" ht="38" customHeight="1">
+      <c r="A15" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>22.83386008460588</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>3.47094459935819</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>8.835349705608206</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>8.835349705608206</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>2.313963066238793</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>0.2073684221440443</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>23.66297549895744</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>-0.829115414351552</v>
+      </c>
+    </row>
+    <row r="16" ht="38" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>22.83386008460588</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>3.47094459935819</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>8.835349705608206</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>8.835349705608206</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>2.313963066238793</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0.4147368442880886</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>23.87034392110148</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>-1.036483836495599</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K16"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>CONDITIONAL SCREEN - NOT ACTUAL FLOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="113" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Assumptions</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>2800 rpm OEM numeric curve; equal sharing among four fans and two parallel filters; density1.2; guard K1.5 each; plenum K1.5 and installation K1 on fan-aperture velocity. Reducer K0.5/1/2. Loss coefficients unverified; reducer/plenum may overlap. Static/installed compatibility unresolved. No loaded filter curve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Filter data</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>No measured clean or loaded curve; allowance is not actual loss</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -779,7 +1464,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14742,6 +15427,1438 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:J14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="23.4" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="24.05" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="42.9" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="20.15" customWidth="1" min="9" max="9"/>
+    <col width="17.55" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Responsible_role_not_assigned_person</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Required_work</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Closure_evidence</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Reviewer_name</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Disposition</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence_file</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="53" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>M01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>OPEN INTERNAL</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Guard strength and reach</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Select material and justified load/probe criteria; assess perforations, welds, side seams and attachments; verify unpowered sample.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Annotated calculation/drawing plus signed inspection result</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="53" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>M02</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>OPEN INTERNAL</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Cabinet joints and stability</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Check plywood/cleat grade, bolt bearing, edge distances, wood screw withdrawal, feet, whole mass/CG and cable pull; no lifting by lid.</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Approved structural details and stability test record</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="53" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>M03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>MIXED INPUT</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Filter seal and service</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Confirm exact filter frame/tolerance, gasket force/compression, flatness and feedthrough seals; verify safe supported removal.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Revised stops/retainers and fit/leak evidence</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="53" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>M04</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Mechanical and electrical</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>WAITING OEM</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Fan harness and protected entry</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>ARCTIC and Noctua connector/cable dimensions pending; Noctua220175. Complete insert, clamp, bend and retention design when received.</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>OEM evidence and updated integrated CAD/drawing</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="53" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Electrical and mechanical</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>OPEN INTERNAL</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Hazard and protective function</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Determine applicable requirements; reconcile fixed guards, isolated servicing and present restart requirements before choosing circuitry.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Signed functional allocation and explicit requirement disposition</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="53" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>OPEN INTERNAL</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Rated circuit and enclosure</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Select DC switching/protection/isolation, wire ratings, verified connectors and enclosure; check startup and auxiliary loads. No terminal guesses.</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Circuit, cable schedule, ratings and physical layout</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="53" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>SITE AND PHYSICAL</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Commissioning</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Verify site supply and OEM adapter suitability; test isolation, stop/restart, supply recovery, abnormal/thermal behaviour under approved procedures.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Signed commissioning record before performance tests</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="53" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Mechanical and test lead</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>PHYSICAL DATA</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Filter duty</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Obtain exact clean/loaded curve or safe measured pressure/flow points; include all installed losses.</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Accepted operating point with margin and replacement rule</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10" ht="53" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>T01</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Test lead and project lead</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>TEAM DECISION</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Acceptance targets and room</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Agree indoor premises, measured flow/noise targets, room volume, instrument methods and PM test plan before trials.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Approved test plan and thresholds</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="53" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Test lead</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>AFTER RELEASE</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Measured prototype results</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Measure airflow, filter losses, bypass, noise, power and room PM with background/control observations.</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Raw logs, calibration references and reviewed results</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="53" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Project lead and engineers</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>AFTER REVIEW</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Procurement and change control</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Confirm exact SKUs, quantities, real quotes, lead times and service scopes; authorize only released lines.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Approved BOM and revision-specific purchase/build authorization</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="53" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>O01</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Separate future project</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>OUT OF INDOOR SCOPE</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Public outdoor tower</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Heat/rain/corrosion/tampering/anchoring and wind-dependent benefit require separate design and field validation.</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Separate outdoor release; no bubble radius claimed</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="38" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Digital preparation</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>CLOSED DIGITAL ONLY</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>E04 assumed service-volume collisions</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Actual dimensions/wiring remain E02 release scope</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>CURRENT_CONTROL_CHECKS.json; unchanged reservations mutually clear</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>DIGITAL PASS / NO BUILD RELEASE</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>CURRENT_CONTROL_CHECKS.json</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J14"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17.55" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Xmin</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Ymin</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Zmin</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Xmax</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ymax</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Zmax</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CB1_SIMPLIFIED_ENVELOPE</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>-150.0</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>-100.0</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>-70.08</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>ORIGINAL APPROXIMATE SHELL; not Hammond manufacturing geometry</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>PL1_SIMPLIFIED_PANEL</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>-142.5</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>-92.5</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>-60.0</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>-58.3744</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>OEM285x185 outline; simplified rectangular proxy, contour/holes omitted except2 proposed4.5mm holes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>DIN1_ENVELOPE</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>-135.0</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>-17.5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-58.3744</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-10.0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17.5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>-50.8744</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>OEM35x7.5 profile envelope; proposed125mm cut, not full profile or approved attachment</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>CTRL1_OPTA_LITE</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>-115.0</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>-44.4</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>-50.8744</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>-45.0</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>44.4</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>10.2256</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>OEM BODY DIMENSIONS / ASSUMED POSITION, ORIENTATION AND MOUNT; no connector geometry</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>H1_NA_FH1</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>-15.0</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>-70.00000000000001</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-53.3744</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28.00000000000003</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>-40.8744</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>OEM BODY DIMENSIONS / ASSUMED POSITION, ORIENTATION AND MOUNT; no connector geometry</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>SC1_NA_FC1</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>-53.3744</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>116.0</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>-32.3744</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>OEM BODY DIMENSIONS / ASSUMED POSITION, ORIENTATION AND MOUNT; no connector geometry</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CTRL1_WIRE_SPACE_ASSUMED</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>-125.0</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>-64.4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-50.8744</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-35.0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>64.4</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>10.2256</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>ASSUMED routing/service volume; actual connectors/clip release and bends unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="38" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>H1_CONNECTOR_SPACE_ASSUMED</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>-35.0</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>-80.00000000000001</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>-53.3744</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>48.00000000000003</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>33.00000000000001</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>-25.8744</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>ASSUMED routing/service volume; actual connectors/clip release and bends unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="38" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SC1_CONNECTOR_SPACE_ASSUMED</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>-85.0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-53.3744</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>-20.0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>-17.3744</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>ASSUMED routing/service volume; actual connectors/clip release and bends unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="38" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>START_FACE_PROXY</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>-29.5</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>40.5</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>69.5</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>29mm head width from OEM; round face and 8mm projection ASSUMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="38" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>START_REAR_ASSUMED</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>-35.0</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-9.0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>46.0</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>ASSUMED40x40x55 below inner lid; not assembled OEM dimensions</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="38" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>START_WIRE_TAIL_ASSUMED</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>-35.0</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>-29.0</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>-9.0</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>ASSUMED20mm additional depth; not verified bend radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="38" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>STOP_FACE_PROXY</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>30.5</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>40.5</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>59.5</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>69.5</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>29mm head width from OEM; round face and 8mm projection ASSUMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="38" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>STOP_REAR_ASSUMED</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>-9.0</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>46.0</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>ASSUMED40x40x55 below inner lid; not assembled OEM dimensions</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="38" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>STOP_WIRE_TAIL_ASSUMED</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-29.0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>-9.0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>ASSUMED20mm additional depth; not verified bend radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="38" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>RESET_FACE_PROXY</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>40.5</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>119.5</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>69.5</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>29mm head width from OEM; round face and 8mm projection ASSUMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="38" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>RESET_REAR_ASSUMED</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-9.0</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>46.0</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>ASSUMED40x40x55 below inner lid; not assembled OEM dimensions</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="38" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>RESET_WIRE_TAIL_ASSUMED</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>-29.0</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>-9.0</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>ASSUMED20mm additional depth; not verified bend radius</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H19"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -15296,7 +17413,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15830,683 +17947,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:K16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>total_m3h</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>per_filter_m3h</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>reducer_K</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>fan_Pa</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>plenum_Pa</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>inner_guard_Pa</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>outer_guard_Pa</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>installation_Pa</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>reducer_Pa</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>nonfilter_Pa</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>filter_allowance_Pa</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="38" customHeight="1">
-      <c r="A2" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>32.59998230680289</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.8677361498395474</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>2.208837426402051</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>2.208837426402051</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>0.5784907665596982</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>0.02592105276800554</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>5.889822821971354</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>26.71015948483153</v>
-      </c>
-    </row>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>32.59998230680289</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0.8677361498395474</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>2.208837426402051</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>2.208837426402051</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>0.5784907665596982</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>0.05184210553601108</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>5.915743874739359</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>26.68423843206353</v>
-      </c>
-    </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>32.59998230680289</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.8677361498395474</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>2.208837426402051</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>2.208837426402051</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>0.5784907665596982</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>0.1036842110720222</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>5.967585980275371</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>26.63239632652752</v>
-      </c>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>30.09391027851171</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>1.355837734124293</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>3.451308478753206</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>3.451308478753206</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>0.9038918227495287</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>0.04050164495000866</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>9.202848159330243</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>20.89106211918147</v>
-      </c>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="2" t="n">
-        <v>250</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>125</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>30.09391027851171</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>1.355837734124293</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>3.451308478753206</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>3.451308478753206</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0.9038918227495287</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0.08100328990001732</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>9.243349804280252</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>20.85056047423146</v>
-      </c>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>30.09391027851171</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>1.355837734124293</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>3.451308478753206</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>3.451308478753206</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>0.9038918227495287</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>0.1620065798000346</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>9.324353094180269</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>20.76955718433144</v>
-      </c>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>27.62649553528014</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>1.952406337138982</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>4.969884209404615</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>4.969884209404615</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>1.301604224759321</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>0.05832236872801246</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>13.25210134943555</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>14.3743941858446</v>
-      </c>
-    </row>
-    <row r="9" ht="38" customHeight="1">
-      <c r="A9" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>27.62649553528014</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>1.952406337138982</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>4.969884209404615</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>4.969884209404615</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>1.301604224759321</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>0.1166447374560249</v>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>13.31042371816356</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>14.31607181711659</v>
-      </c>
-    </row>
-    <row r="10" ht="38" customHeight="1">
-      <c r="A10" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>27.62649553528014</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>1.952406337138982</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>4.969884209404615</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>4.969884209404615</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>1.301604224759321</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0.2332894749120498</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>13.42706845561958</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>14.19942707966056</v>
-      </c>
-    </row>
-    <row r="11" ht="38" customHeight="1">
-      <c r="A11" s="3" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>25.26773196530823</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>2.657441958883614</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>6.764564618356284</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>6.764564618356284</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>1.771627972589076</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>0.07938322410201697</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>18.03758239228728</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>7.230149573020956</v>
-      </c>
-    </row>
-    <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="2" t="n">
-        <v>350</v>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>175</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>25.26773196530823</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>2.657441958883614</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>6.764564618356284</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>6.764564618356284</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>1.771627972589076</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>0.1587664482040339</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>18.11696561638929</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>7.150766348918939</v>
-      </c>
-    </row>
-    <row r="13" ht="38" customHeight="1">
-      <c r="A13" s="3" t="n">
-        <v>350</v>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>25.26773196530823</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>2.657441958883614</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>6.764564618356284</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>6.764564618356284</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>1.771627972589076</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>0.3175328964080679</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>18.27573206459333</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>6.991999900714905</v>
-      </c>
-    </row>
-    <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>22.83386008460588</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>3.47094459935819</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>8.835349705608206</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>8.835349705608206</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>2.313963066238793</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>0.1036842110720222</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>23.55929128788542</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>-0.7254312032795305</v>
-      </c>
-    </row>
-    <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>22.83386008460588</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>3.47094459935819</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>8.835349705608206</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>8.835349705608206</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>2.313963066238793</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>0.2073684221440443</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>23.66297549895744</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>-0.829115414351552</v>
-      </c>
-    </row>
-    <row r="16" ht="38" customHeight="1">
-      <c r="A16" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>22.83386008460588</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>3.47094459935819</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>8.835349705608206</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>8.835349705608206</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>2.313963066238793</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>0.4147368442880886</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>23.87034392110148</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>-1.036483836495599</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:K16"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>CONDITIONAL SCREEN - NOT ACTUAL FLOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="113" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Assumptions</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>2800 rpm OEM numeric curve; equal sharing among four fans and two parallel filters; density1.2; guard K1.5 each; plenum K1.5 and installation K1 on fan-aperture velocity. Reducer K0.5/1/2. Loss coefficients unverified; reducer/plenum may overlap. Static/installed compatibility unresolved. No loaded filter curve.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Filter data</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>No measured clean or loaded curve; allowance is not actual loss</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:B4"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/reports/shareable_20261005/technical/TECHNICAL_REVIEW.xlsx
+++ b/reports/shareable_20261005/technical/TECHNICAL_REVIEW.xlsx
@@ -12,17 +12,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claims" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Room scenarios" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funding quotes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Current release gates" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control module placement" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release decisions" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parts register" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pressure screening" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pressure assumptions" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fasteners" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Display dimensions" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Current combined parts" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Current release gates" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control module placement" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release decisions" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parts register" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pressure screening" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pressure assumptions" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fasteners" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Display dimensions" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read me'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read me'!$A$1:$B$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Read me'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Milestones'!$A$1:$D$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Milestones'!$1:$1</definedName>
@@ -30,24 +31,26 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Claims'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Room scenarios'!$A$1:$H$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Room scenarios'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Funding quotes'!$A$1:$M$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Funding quotes'!$A$1:$M$29</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Funding quotes'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Current release gates'!$A$1:$J$14</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Current release gates'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Control module placement'!$A$1:$H$19</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Control module placement'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Release decisions'!$A$1:$J$13</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Release decisions'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Parts register'!$A$1:$F$16</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Parts register'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Pressure screening'!$A$1:$K$16</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Pressure screening'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Pressure assumptions'!$A$1:$B$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Pressure assumptions'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Fasteners'!$A$1:$D$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="11">'Fasteners'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Display dimensions'!$A$1:$F$494</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="12">'Display dimensions'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Current combined parts'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Current combined parts'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Current release gates'!$A$1:$J$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Current release gates'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Control module placement'!$A$1:$H$19</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Control module placement'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Release decisions'!$A$1:$J$13</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Release decisions'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Parts register'!$A$1:$F$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Parts register'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Pressure screening'!$A$1:$K$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Pressure screening'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Pressure assumptions'!$A$1:$B$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'Pressure assumptions'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Fasteners'!$A$1:$D$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'Fasteners'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Display dimensions'!$A$1:$F$494</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'Display dimensions'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -498,7 +501,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="38" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Revision</t>
@@ -506,7 +509,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>D01 R03M / IH02 / 5 October 2026</t>
+          <t>D01 R03M / E05 / current parallel batch / 5 October 2026</t>
         </is>
       </c>
     </row>
@@ -522,50 +525,598 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="38" customHeight="1">
+    <row r="4" ht="68" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>Current parts</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Funding quotes and Current combined parts use28 current references; other parts/release tabs are historical snapshots. Verify quote unit/kit basis before entering quantity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
           <t>Prices</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Blank means UNKNOWN; no prices have been invented.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>CAD/digital checks are not physical results.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>College/NGO funding; no college lab assumed; qualified physical services still needed.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="35.1" customWidth="1" min="3" max="3"/>
+    <col width="17.55" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="24.05" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Quantity_basis</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence_status</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Unresolved</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>F1-F4</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>ARCTIC P14 Max ACFAN00287A</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Exact OEM reference</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Delivered revision and cable details; guard and duty integration</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Electrical BOM; OEM sources S1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="53" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>FL1-FL2</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>IKEA STARKVIND104.633.30 particle filter</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Experimental reference only</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>370x290x40 catalogue envelope; pressure curve/frame/seal tolerances unknown; OEM specifies STARKVIND use only</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>r02_adapter/README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>PS1</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Noctua NV-PS1 with NA-AC10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Exact OEM reference</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12V2A24W; startup/auxiliary/site suitability not closed</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Electrical BOM S2/S6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Noctua NA-FC1</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Exact OEM reference</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Speed controller is not protective isolation</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Electrical BOM S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Noctua NA-FH1 with NA-EC1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Exact OEM reference</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24W selected input; self-reset; only port1 RPM upstream; SATA unused</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Electrical BOM S4/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>EXT</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>2 candidate leads</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>NA-EC1 300mm from NA-SEC1 kit</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Candidate not selected</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Kit contains3 leads; dimensions pending; check total connection count before purchase</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Harness README</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>1 assembly</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>R03M panels and cleats</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Custom proposed geometry</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Grade/joints/strength/finish unreleased; panel inventory is controlling geometry</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>CAD_PART_INVENTORY.csv and15 DXFs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="38" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>GUARD</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>2 assemblies</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>R03M welded perforated guards</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Custom proposed geometry</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Strength/reach/weld criteria unreleased;1mm not approved</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>GUARD_BLANKS.csv; guard_pattern.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="38" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>FIX</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>1 scheduled set</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>R03M fasteners and compression limiters</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Proposed geometry</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Use FASTENER_SCHEDULE; do not add inventory quantities again; grade/torque unresolved</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>FASTENER_SCHEDULE.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="38" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>SEAL</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>1 design set</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Filter/fan/penetration seals</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Unselected material</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Gasket dimensions are installed envelopes, not a compression specification</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>CAD inventory; mechanical_screen.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="38" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>FEET</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Retained feet</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Proposed geometry</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Material/bearing/stability not released</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical package</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="38" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>PR1</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>1 assembly</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Protection and service isolation</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>UNSELECTED</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Not replaced by hub fuse, PWM or software model</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Electrical interfaces J09/J11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="38" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>BOX</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>1 assembly</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Controls enclosure and cable restraints</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>UNSELECTED</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>140x100x40 reservation is not selected enclosure or complete fit</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Electrical package</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="38" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>TEST</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>1 service scope</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated airflow/pressure/power/noise/PM measurement</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>UNSELECTED</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Rent or commission test service; no college lab assumed</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Validation package</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="38" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>1 service scope</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Fabrication assembly and qualified review</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>UNSELECTED</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Internal engineers review; outsource workshop work as needed</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Review register</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F16"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1176,7 +1727,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1244,7 +1795,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1464,7 +2015,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14831,19 +15382,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="35.1" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="27.95" customWidth="1" min="2" max="2"/>
+    <col width="17.55" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="22.1" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
@@ -14916,7 +15467,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="38" customHeight="1">
+    <row r="2" ht="53" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>F1-F4</t>
@@ -14924,7 +15475,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ARCTIC P14 Max ACFAN00287A</t>
+          <t>ARCTIC P14 Max black ACFAN00287A</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -14936,7 +15487,11 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Delivered revision,cable/connector dimensions,installed duty,guards and protection; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -14948,7 +15503,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" ht="38" customHeight="1">
+    <row r="3" ht="53" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>FL1-FL2</t>
@@ -14956,7 +15511,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>IKEA STARKVIND104.633.30 particle filter</t>
+          <t>IKEA STARKVIND104.633.30 particle filters</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
@@ -14968,7 +15523,11 @@
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Actual tolerances,frame,seals,clean/loaded resistance; OEM specifies STARKVIND use; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -14980,7 +15539,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="38" customHeight="1">
+    <row r="4" ht="53" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>PS1</t>
@@ -15000,7 +15559,11 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Actual startup/auxiliary demand,fault coordination,site suitability; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -15012,15 +15575,15 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="38" customHeight="1">
+    <row r="5" ht="53" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>SC1</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Noctua NA-FC1</t>
+          <t>Noctua NA-FH1 with supplied NA-EC1</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -15032,7 +15595,11 @@
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Actual connector fit,retained carrier,cable capacity,abnormal restart behaviour; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -15044,15 +15611,15 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="38" customHeight="1">
+    <row r="6" ht="53" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>SC1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Noctua NA-FH1 with NA-EC1</t>
+          <t>Noctua NA-FC1</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -15064,7 +15631,11 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Actual mounting,connectors,heat; no live knob interface designed; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -15076,7 +15647,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="38" customHeight="1">
+    <row r="7" ht="68" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>EXT</t>
@@ -15084,12 +15655,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>NA-EC1 300mm from NA-SEC1 kit</t>
+          <t>Noctua NA-EC1 from NA-SEC1 kit</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>2 candidate leads</t>
+          <t>2 candidate extension leads</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr"/>
@@ -15098,7 +15669,11 @@
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Exact lead count and connector/gland fit pending;do not duplicate supplied hub lead; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -15110,21 +15685,19 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="38" customHeight="1">
+    <row r="8" ht="53" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>CTRL1</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>R03M panels and cleats</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1 assembly</t>
-        </is>
+          <t>Arduino Opta Lite AFX00003</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
@@ -15132,7 +15705,11 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Protective functions not implemented or validated; no upload/physical test; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -15144,21 +15721,19 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="38" customHeight="1">
+    <row r="9" ht="53" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>GUARD</t>
+          <t>CB1</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>R03M welded perforated guards</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>2 assemblies</t>
-        </is>
+          <t>Hammond1554XA2GY</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
@@ -15166,7 +15741,11 @@
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Whole mounting,entries,thermal,modified ingress,protection and actual fit; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -15178,21 +15757,19 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="38" customHeight="1">
+    <row r="10" ht="53" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>FIX</t>
+          <t>PL1</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>R03M fasteners and compression limiters</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1 scheduled set</t>
-        </is>
+          <t>Hammond1554XPL</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
@@ -15200,7 +15777,11 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Delivered thickness,edge contour,holes,fasteners,functional earth/metal treatment; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -15212,20 +15793,20 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="38" customHeight="1">
+    <row r="11" ht="68" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>SEAL</t>
+          <t>DIN1</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Filter/fan/penetration seals</t>
+          <t>35x7.5mm rail;Phoenix0801733 reference</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>1 design set</t>
+          <t>1 proposed125mm cut</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr"/>
@@ -15234,7 +15815,11 @@
       <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Obtain suitable cut piece;reference catalogue pack is not procurement quantity;attachment unapproved; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
       <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="inlineStr">
         <is>
@@ -15246,19 +15831,19 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="38" customHeight="1">
+    <row r="12" ht="53" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FEET</t>
+          <t>PB_START</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Retained feet</t>
+          <t>Schneider ZB5AA3 green spring-return head</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
@@ -15266,7 +15851,11 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Actual full stack,labels,torque,retention,sealing; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
@@ -15278,21 +15867,19 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="38" customHeight="1">
+    <row r="13" ht="53" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>PR1</t>
+          <t>PB_STOP</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Protection and service isolation</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>1 assembly</t>
-        </is>
+          <t>Schneider ZB5AA4 red spring-return head</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
       <c r="E13" s="3" t="inlineStr"/>
@@ -15300,7 +15887,11 @@
       <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr"/>
       <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Not emergency stop,isolation or protective restart; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
       <c r="K13" s="3" t="inlineStr"/>
       <c r="L13" s="3" t="inlineStr">
         <is>
@@ -15312,21 +15903,19 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="38" customHeight="1">
+    <row r="14" ht="53" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>PB_RESET</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Controls enclosure and cable restraints</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>1 assembly</t>
-        </is>
+          <t>Schneider ZB5AA6 blue spring-return head</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
@@ -15334,7 +15923,11 @@
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Reset is not start or protective restart approval; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -15346,21 +15939,19 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="38" customHeight="1">
+    <row r="15" ht="53" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>TEST</t>
+          <t>PB_COLLAR</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Calibrated airflow/pressure/power/noise/PM measurement</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>1 service scope</t>
-        </is>
+          <t>Schneider ZB5AZ009 fixing collar</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="D15" s="3" t="inlineStr"/>
       <c r="E15" s="3" t="inlineStr"/>
@@ -15368,7 +15959,11 @@
       <c r="G15" s="3" t="inlineStr"/>
       <c r="H15" s="3" t="inlineStr"/>
       <c r="I15" s="3" t="inlineStr"/>
-      <c r="J15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Delivered mounting stack and required accessories; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
       <c r="K15" s="3" t="inlineStr"/>
       <c r="L15" s="3" t="inlineStr">
         <is>
@@ -15380,21 +15975,19 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="38" customHeight="1">
+    <row r="16" ht="53" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>BUILD</t>
+          <t>PB_NO</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Fabrication assembly and qualified review</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>1 service scope</t>
-        </is>
+          <t>Schneider ZBE1016 gold-flashed NO contact</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
@@ -15402,7 +15995,11 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Numeric minimum switching range,actual terminal identifiers,branch protection; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
@@ -15414,8 +16011,498 @@
         <v/>
       </c>
     </row>
+    <row r="17" ht="53" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>PB_NC</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Schneider ZBE1026 gold-flashed NC contact</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Numeric minimum switching range,actual terminal identifiers,branch protection; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>UNQUOTED / NOT ORDER AUTHORIZATION</t>
+        </is>
+      </c>
+      <c r="M17" s="3">
+        <f>IF(AND(ISNUMBER(C17),ISNUMBER(F17),ISNUMBER(G17),ISNUMBER(H17)),C17*F17+SUM(G17:H17),"UNQUOTED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="68" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>PR1</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Independent protection and isolation</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1 functional assembly</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Rated circuit and hazard allocation;ordinary controls/Opta/hub fuse do not substitute; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>UNQUOTED / NOT ORDER AUTHORIZATION</t>
+        </is>
+      </c>
+      <c r="M18" s="2">
+        <f>IF(AND(ISNUMBER(C18),ISNUMBER(F18),ISNUMBER(G18),ISNUMBER(H18)),C18*F18+SUM(G18:H18),"UNQUOTED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="68" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>FUSE</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>DC fuse and compatible holder</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Quantity unknown</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Fault-time coordination,temperature,contacts and source startup;not a selected fuse; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>UNQUOTED / NOT ORDER AUTHORIZATION</t>
+        </is>
+      </c>
+      <c r="M19" s="3">
+        <f>IF(AND(ISNUMBER(C19),ISNUMBER(F19),ISNUMBER(G19),ISNUMBER(H19)),C19*F19+SUM(G19:H19),"UNQUOTED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="53" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TERM</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Terminals branch protection and wire system</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Quantity unknown</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Sizes,current/fault/temperature ratings,OEM connectors and label schedule; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>UNQUOTED / NOT ORDER AUTHORIZATION</t>
+        </is>
+      </c>
+      <c r="M20" s="2">
+        <f>IF(AND(ISNUMBER(C20),ISNUMBER(F20),ISNUMBER(G20),ISNUMBER(H20)),C20*F20+SUM(G20:H20),"UNQUOTED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="53" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Protected cable entries glands inserts and clamps</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Quantity unknown</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Insert size,lead bends,retention,feedthrough seal and guard interface; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>UNQUOTED / NOT ORDER AUTHORIZATION</t>
+        </is>
+      </c>
+      <c r="M21" s="3">
+        <f>IF(AND(ISNUMBER(C21),ISNUMBER(F21),ISNUMBER(G21),ISNUMBER(H21)),C21*F21+SUM(G21:H21),"UNQUOTED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="53" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>MOUNT</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Control box retained mounting and component carriers</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>1 mounting set</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Actual support hardware,box placement,tower attachment,service clearance; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>UNQUOTED / NOT ORDER AUTHORIZATION</t>
+        </is>
+      </c>
+      <c r="M22" s="2">
+        <f>IF(AND(ISNUMBER(C22),ISNUMBER(F22),ISNUMBER(G22),ISNUMBER(H22)),C22*F22+SUM(G22:H22),"UNQUOTED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="53" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>R03M493-object cabinet geometry</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>1 assembly</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>Material grade,joint strength,whole mass/CG,stability; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>UNQUOTED / NOT ORDER AUTHORIZATION</t>
+        </is>
+      </c>
+      <c r="M23" s="3">
+        <f>IF(AND(ISNUMBER(C23),ISNUMBER(F23),ISNUMBER(G23),ISNUMBER(H23)),C23*F23+SUM(G23:H23),"UNQUOTED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="53" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>GUARD</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>R03M perforated guards</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2 assemblies</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Perforated strength,reach,side seam and attachment criteria; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>UNQUOTED / NOT ORDER AUTHORIZATION</t>
+        </is>
+      </c>
+      <c r="M24" s="2">
+        <f>IF(AND(ISNUMBER(C24),ISNUMBER(F24),ISNUMBER(G24),ISNUMBER(H24)),C24*F24+SUM(G24:H24),"UNQUOTED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="53" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>FIX</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>R03M fasteners and compression limiters</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>One scheduled set</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>Actual grades,torques,bearing,withdrawal and tolerances; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>UNQUOTED / NOT ORDER AUTHORIZATION</t>
+        </is>
+      </c>
+      <c r="M25" s="3">
+        <f>IF(AND(ISNUMBER(C25),ISNUMBER(F25),ISNUMBER(G25),ISNUMBER(H25)),C25*F25+SUM(G25:H25),"UNQUOTED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="53" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>SEAL</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Filter fan and penetration gaskets</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>One design set</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Force-compression curves,flatness,tolerances,bypass and closure loads; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>UNQUOTED / NOT ORDER AUTHORIZATION</t>
+        </is>
+      </c>
+      <c r="M26" s="2">
+        <f>IF(AND(ISNUMBER(C26),ISNUMBER(F26),ISNUMBER(G26),ISNUMBER(H26)),C26*F26+SUM(G26:H26),"UNQUOTED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="53" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>FEET</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>R03M retained feet</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr"/>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>Material,retention,bearing,complete stability and cable-pull evidence; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr"/>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>UNQUOTED / NOT ORDER AUTHORIZATION</t>
+        </is>
+      </c>
+      <c r="M27" s="3">
+        <f>IF(AND(ISNUMBER(C27),ISNUMBER(F27),ISNUMBER(G27),ISNUMBER(H27)),C27*F27+SUM(G27:H27),"UNQUOTED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="53" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>TEST</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Calibrated airflow pressure power noise PM tests</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>One service scope</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Exact methods,instruments,room and acceptance thresholds; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>UNQUOTED / NOT ORDER AUTHORIZATION</t>
+        </is>
+      </c>
+      <c r="M28" s="2">
+        <f>IF(AND(ISNUMBER(C28),ISNUMBER(F28),ISNUMBER(G28),ISNUMBER(H28)),C28*F28+SUM(G28:H28),"UNQUOTED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="53" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Qualified fabrication assembly and commissioning</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>One service scope</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>Real quotes,review scope,procurement authorization and signed physical results; quantities are proposals, verify kit/unit basis before quotation</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>UNQUOTED / NOT ORDER AUTHORIZATION</t>
+        </is>
+      </c>
+      <c r="M29" s="3">
+        <f>IF(AND(ISNUMBER(C29),ISNUMBER(F29),ISNUMBER(G29),ISNUMBER(H29)),C29*F29+SUM(G29:H29),"UNQUOTED")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M16"/>
+  <autoFilter ref="A1:M29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -15427,19 +16514,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="23.4" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="24.05" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="42.9" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="20.15" customWidth="1" min="9" max="9"/>
-    <col width="17.55" customWidth="1" min="10" max="10"/>
+    <col width="17.55" customWidth="1" min="2" max="2"/>
+    <col width="27.95" customWidth="1" min="3" max="3"/>
+    <col width="34.45" customWidth="1" min="4" max="4"/>
+    <col width="48.1" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="53.95" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15450,586 +16534,1783 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Responsible_role_not_assigned_person</t>
+          <t>Quantity_basis</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Exact_product_or_geometry</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Required_work</t>
+          <t>Known_basis</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Closure_evidence</t>
+          <t>Not_released_or_unknown</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Reviewer_name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Disposition</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Evidence_file</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="53" customHeight="1">
+          <t>Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>M01</t>
+          <t>F1-F4</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Mechanical</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>OPEN INTERNAL</t>
+          <t>ARCTIC P14 Max black ACFAN00287A</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Guard strength and reach</t>
+          <t>VERIFIED OEM REFERENCE / NOT PURCHASE RELEASE</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Select material and justified load/probe criteria; assess perforations, welds, side seams and attachments; verify unpowered sample.</t>
+          <t>140x140x27mm;12V;0.35A each;245g;0-40C OEM ambient</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Annotated calculation/drawing plus signed inspection result</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="53" customHeight="1">
+          <t>Delivered revision,cable/connector dimensions,installed duty,guards and protection</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/component_validation/README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="38" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>M02</t>
+          <t>FL1-FL2</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Mechanical</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>OPEN INTERNAL</t>
+          <t>IKEA STARKVIND104.633.30 particle filters</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Cabinet joints and stability</t>
+          <t>EXPERIMENTAL REFERENCE / NOT CUSTOM-USE APPROVAL</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Check plywood/cleat grade, bolt bearing, edge distances, wood screw withdrawal, feet, whole mass/CG and cable pull; no lifting by lid.</t>
+          <t>370x290x40mm catalogue envelope</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Approved structural details and stability test record</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="53" customHeight="1">
+          <t>Actual tolerances,frame,seals,clean/loaded resistance; OEM specifies STARKVIND use</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/r02_adapter/README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="38" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>M03</t>
+          <t>PS1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Mechanical</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>MIXED INPUT</t>
+          <t>Noctua NV-PS1 with NA-AC10</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Filter seal and service</t>
+          <t>VERIFIED OEM REFERENCE / NOT PURCHASE RELEASE</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Confirm exact filter frame/tolerance, gasket force/compression, flatness and feedthrough seals; verify safe supported removal.</t>
+          <t>External12V2A24W adapter</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Revised stops/retainers and fit/leak evidence</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5" ht="53" customHeight="1">
+          <t>Actual startup/auxiliary demand,fault coordination,site suitability</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/electrical_package/POWER_COORDINATION.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="38" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>M04</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Mechanical and electrical</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>WAITING OEM</t>
+          <t>Noctua NA-FH1 with supplied NA-EC1</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Fan harness and protected entry</t>
+          <t>VERIFIED OEM REFERENCE / NOT PROTECTIVE DEVICE</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>ARCTIC and Noctua connector/cable dimensions pending; Noctua220175. Complete insert, clamp, bend and retention design when received.</t>
+          <t>Selected4-pin path24W2A;93x43x12.5mm body</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>OEM evidence and updated integrated CAD/drawing</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6" ht="53" customHeight="1">
+          <t>Actual connector fit,retained carrier,cable capacity,abnormal restart behaviour</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/electrical_package/control_module/CURRENT_CONTROL_CHECKS.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>SC1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Electrical and mechanical</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>OPEN INTERNAL</t>
+          <t>Noctua NA-FC1</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Hazard and protective function</t>
+          <t>VERIFIED OEM REFERENCE / NOT ISOLATION</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Determine applicable requirements; reconcile fixed guards, isolated servicing and present restart requirements before choosing circuitry.</t>
+          <t>3A maximum;21x25x48mm body; isolated-preset proposal</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Signed functional allocation and explicit requirement disposition</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7" ht="53" customHeight="1">
+          <t>Actual mounting,connectors,heat; no live knob interface designed</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/electrical_package/control_module/README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="38" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>EXT</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>2 candidate extension leads</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>OPEN INTERNAL</t>
+          <t>Noctua NA-EC1 from NA-SEC1 kit</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Rated circuit and enclosure</t>
+          <t>CANDIDATE / UNSELECTED</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Select DC switching/protection/isolation, wire ratings, verified connectors and enclosure; check startup and auxiliary loads. No terminal guesses.</t>
+          <t>300mm;NA-SEC1 kit has3 leads</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Circuit, cable schedule, ratings and physical layout</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="53" customHeight="1">
+          <t>Exact lead count and connector/gland fit pending;do not duplicate supplied hub lead</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/mechanical_package/harness_detail/README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="38" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>CTRL1</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>SITE AND PHYSICAL</t>
+          <t>Arduino Opta Lite AFX00003</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Commissioning</t>
+          <t>VERIFIED OEM REFERENCE / ORDINARY BENCH ONLY</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Verify site supply and OEM adapter suitability; test isolation, stop/restart, supply recovery, abnormal/thermal behaviour under approved procedures.</t>
+          <t>70x88.8mm front;61.1mm reserved depth;12-24V;max2W;target compile verified</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Signed commissioning record before performance tests</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9" ht="53" customHeight="1">
+          <t>Protective functions not implemented or validated; no upload/physical test</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/electrical_package/OPTA_BOARD_BUILD.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="38" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>CB1</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Mechanical and test lead</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>PHYSICAL DATA</t>
+          <t>Hammond1554XA2GY</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Filter duty</t>
+          <t>VERIFIED OEM REFERENCE / MODIFIED ASSEMBLY UNRELEASED</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Obtain exact clean/loaded curve or safe measured pressure/flow points; include all installed losses.</t>
+          <t>Nominal300x200x120mm external box;24-solid private OEM STEP</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Accepted operating point with margin and replacement rule</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10" ht="53" customHeight="1">
+          <t>Whole mounting,entries,thermal,modified ingress,protection and actual fit</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/electrical_package/control_module/CURRENT_CONTROL_CHECKS.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="38" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>T01</t>
+          <t>PL1</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Test lead and project lead</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>TEAM DECISION</t>
+          <t>Hammond1554XPL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Acceptance targets and room</t>
+          <t>VERIFIED OEM REFERENCE / DRILLING UNRELEASED</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Agree indoor premises, measured flow/noise targets, room volume, instrument methods and PM test plan before trials.</t>
+          <t>285x185mm panel;STEP thickness1.6256mm vs catalogue2mm rounding</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Approved test plan and thresholds</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr"/>
+          <t>Delivered thickness,edge contour,holes,fasteners,functional earth/metal treatment</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/electrical_package/control_module/README.md</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="53" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>T02</t>
+          <t>DIN1</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Test lead</t>
+          <t>1 proposed125mm cut</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>AFTER RELEASE</t>
+          <t>35x7.5mm rail;Phoenix0801733 reference</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Measured prototype results</t>
+          <t>CANDIDATE GEOMETRY / UNSELECTED PURCHASE LINE</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Measure airflow, filter losses, bypass, noise, power and room PM with background/control observations.</t>
+          <t>Reference15x6.2mm slots at25mm pitch</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Raw logs, calibration references and reviewed results</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" ht="53" customHeight="1">
+          <t>Obtain suitable cut piece;reference catalogue pack is not procurement quantity;attachment unapproved</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/electrical_package/control_module/README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="38" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>C01</t>
+          <t>PB_START</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Project lead and engineers</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>AFTER REVIEW</t>
+          <t>Schneider ZB5AA3 green spring-return head</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Procurement and change control</t>
+          <t>CANDIDATE / NOT RELEASED</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Confirm exact SKUs, quantities, real quotes, lead times and service scopes; authorize only released lines.</t>
+          <t>22mm class; proposed22.3+0.4/-0 hole;1-6mm panel range</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Approved BOM and revision-specific purchase/build authorization</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13" ht="53" customHeight="1">
+          <t>Actual full stack,labels,torque,retention,sealing</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/electrical_package/control_module/LID_CONTROL_PARTS.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="38" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>O01</t>
+          <t>PB_STOP</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Separate future project</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>OUT OF INDOOR SCOPE</t>
+          <t>Schneider ZB5AA4 red spring-return head</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Public outdoor tower</t>
+          <t>CANDIDATE / ORDINARY STOP ONLY</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Heat/rain/corrosion/tampering/anchoring and wind-dependent benefit require separate design and field validation.</t>
+          <t>Same head family;NC sensing contact proposed</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Separate outdoor release; no bubble radius claimed</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr"/>
+          <t>Not emergency stop,isolation or protective restart</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/electrical_package/control_module/LID_CONTROL_PARTS.csv</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="38" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>D05</t>
+          <t>PB_RESET</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Digital preparation</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>CLOSED DIGITAL ONLY</t>
+          <t>Schneider ZB5AA6 blue spring-return head</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>E04 assumed service-volume collisions</t>
+          <t>CANDIDATE / NOT RELEASED</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Actual dimensions/wiring remain E02 release scope</t>
+          <t>Same head family;NO sensing contact proposed</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>CURRENT_CONTROL_CHECKS.json; unchanged reservations mutually clear</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>DIGITAL PASS / NO BUILD RELEASE</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>CURRENT_CONTROL_CHECKS.json</t>
+          <t>Reset is not start or protective restart approval</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/electrical_package/control_module/LID_CONTROL_PARTS.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="38" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>PB_COLLAR</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Schneider ZB5AZ009 fixing collar</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>CANDIDATE / NOT RELEASED</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>OEM XB5 electrical-block collar reference</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Delivered mounting stack and required accessories</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/electrical_package/control_module/LID_CONTROL_PARTS.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="38" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>PB_NO</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Schneider ZBE1016 gold-flashed NO contact</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>CANDIDATE / NUMERIC LOW-CURRENT SUITABILITY UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Current2026 OEM catalogue low-power designation verified</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Numeric minimum switching range,actual terminal identifiers,branch protection</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/electrical_package/control_module/CURRENT_CONTROL_CHECKS.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="38" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>PB_NC</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Schneider ZBE1026 gold-flashed NC contact</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>CANDIDATE / NUMERIC LOW-CURRENT SUITABILITY UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Current2026 OEM catalogue low-power designation verified</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Numeric minimum switching range,actual terminal identifiers,branch protection</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/electrical_package/control_module/CURRENT_CONTROL_CHECKS.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="38" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>PR1</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>1 functional assembly</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Independent protection and isolation</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>UNSELECTED</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Existing hazard/restart requirements remain open</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Rated circuit and hazard allocation;ordinary controls/Opta/hub fuse do not substitute</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/electrical_package/control_module/CURRENT_RELEASE_GATES.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="38" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>FUSE</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Quantity unknown</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>DC fuse and compatible holder</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>UNSELECTED</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Littelfuse0297002.WXNV2A is screening comparison only</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Fault-time coordination,temperature,contacts and source startup;not a selected fuse</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/electrical_package/OPTA_INTEGRATION_SCREEN.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="38" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TERM</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Quantity unknown</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Terminals branch protection and wire system</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>UNSELECTED</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>No rated terminal/cable assignments released</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Sizes,current/fault/temperature ratings,OEM connectors and label schedule</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/electrical_package/control_module/CURRENT_RELEASE_GATES.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="38" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Quantity unknown</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Protected cable entries glands inserts and clamps</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>UNSELECTED</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>OEM lead/connector envelope enquiries pending</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Insert size,lead bends,retention,feedthrough seal and guard interface</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/mechanical_package/harness_detail/README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="53" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>MOUNT</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>1 mounting set</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Control box retained mounting and component carriers</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>UNSELECTED</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>5mm hub/controller lift and DIN seating are assumed envelopes</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Actual support hardware,box placement,tower attachment,service clearance</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/electrical_package/control_module/CURRENT_CONTROL_CHECKS.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="38" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>1 assembly</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>R03M493-object cabinet geometry</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSED REVIEW CAD / NOT FABRICATION RELEASE</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Native assembly and15 review DXFs controlling geometry</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Material grade,joint strength,whole mass/CG,stability</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/mechanical_package/README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="38" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>GUARD</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2 assemblies</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>R03M perforated guards</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>PROPOSED REVIEW CAD / NOT SAFETY RELEASE</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2822 holes per face;open area0.0354623m2 each</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Perforated strength,reach,side seam and attachment criteria</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/mechanical_package/GUARD_ACCESS_DECISION.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="38" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>FIX</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>One scheduled set</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>R03M fasteners and compression limiters</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSED GEOMETRY / UNRELEASED</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Use FASTENER_SCHEDULE quantities;do not sum inventory duplicates</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Actual grades,torques,bearing,withdrawal and tolerances</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/mechanical_package/FASTENER_SCHEDULE.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="38" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>SEAL</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>One design set</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Filter fan and penetration gaskets</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>UNSELECTED MATERIAL</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Installed geometric envelopes only</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Force-compression curves,flatness,tolerances,bypass and closure loads</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/mechanical_package/README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="38" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>FEET</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>R03M retained feet</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>PROPOSED GEOMETRY / UNRELEASED</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Nominal support geometry extracted digitally</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Material,retention,bearing,complete stability and cable-pull evidence</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/mechanical_package/mass_stability_review.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="38" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>TEST</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>One service scope</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Calibrated airflow pressure power noise PM tests</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>UNSELECTED / NO PHYSICAL DATA</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>No college lab assumed;rent or paid-service route</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Exact methods,instruments,room and acceptance thresholds</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>docs/build/NO_LAB_BUILD_ROUTE.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="38" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>One service scope</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Qualified fabrication assembly and commissioning</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>UNSELECTED</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Funding support only;workshop service not booked</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Real quotes,review scope,procurement authorization and signed physical results</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>reports/prototype_d01/electrical_package/control_module/CURRENT_RELEASE_GATES.csv</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J14"/>
+  <autoFilter ref="A1:G29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="23.4" customWidth="1" min="2" max="2"/>
+    <col width="14.95" customWidth="1" min="3" max="3"/>
+    <col width="35.1" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="42.9" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="26.65" customWidth="1" min="9" max="9"/>
+    <col width="43.55" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Responsible_role_not_assigned_person</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Required_work</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Closure_evidence</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Reviewer_name</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Disposition</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence_file</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="53" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>M01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>OPEN INTERNAL</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Guard strength and reach</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Select material and justified load/probe criteria; assess perforations, welds, side seams and attachments; verify unpowered sample.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Annotated calculation/drawing plus signed inspection result</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="53" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>M02</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>OPEN INTERNAL</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Cabinet joints and stability</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Check plywood/cleat grade, bolt bearing, edge distances, wood screw withdrawal, feet, whole mass/CG and cable pull; no lifting by lid.</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Approved structural details and stability test record</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="53" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>M03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>MIXED INPUT</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Filter seal and service</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Confirm exact filter frame/tolerance, gasket force/compression, flatness and feedthrough seals; verify safe supported removal.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Revised stops/retainers and fit/leak evidence</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="53" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>M04</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Mechanical and electrical</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>WAITING OEM</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Fan harness and protected entry</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>ARCTIC and Noctua connector/cable dimensions pending; Noctua220175. Complete insert, clamp, bend and retention design when received.</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>OEM evidence and updated integrated CAD/drawing</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="53" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Electrical and mechanical</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>OPEN INTERNAL</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Hazard and protective function</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Determine applicable requirements; reconcile fixed guards, isolated servicing and present restart requirements before choosing circuitry.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Signed functional allocation and explicit requirement disposition</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="53" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>OPEN INTERNAL</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Rated circuit and enclosure</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Select DC switching/protection/isolation, wire ratings, verified connectors and enclosure; check startup and auxiliary loads. No terminal guesses.</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Circuit, cable schedule, ratings and physical layout</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="53" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>SITE AND PHYSICAL</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Commissioning</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Verify site supply and OEM adapter suitability; test isolation, stop/restart, supply recovery, abnormal/thermal behaviour under approved procedures.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Signed commissioning record before performance tests</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="53" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Mechanical and test lead</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>PHYSICAL DATA</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Filter duty</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Obtain exact clean/loaded curve or safe measured pressure/flow points; include all installed losses.</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Accepted operating point with margin and replacement rule</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10" ht="53" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>T01</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Test lead and project lead</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>TEAM DECISION</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Acceptance targets and room</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Agree indoor premises, measured flow/noise targets, room volume, instrument methods and PM test plan before trials.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Approved test plan and thresholds</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="53" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Test lead</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>AFTER RELEASE</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Measured prototype results</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Measure airflow, filter losses, bypass, noise, power and room PM with background/control observations.</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Raw logs, calibration references and reviewed results</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="53" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Project lead and engineers</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>AFTER REVIEW</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Procurement and change control</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Confirm exact SKUs, quantities, real quotes, lead times and service scopes; authorize only released lines.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Approved BOM and revision-specific purchase/build authorization</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="53" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>O01</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Separate future project</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>OUT OF INDOOR SCOPE</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Public outdoor tower</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Heat/rain/corrosion/tampering/anchoring and wind-dependent benefit require separate design and field validation.</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Separate outdoor release; no bubble radius claimed</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="38" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Digital preparation</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>CLOSED DIGITAL ONLY</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>E04 assumed service-volume collisions</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Actual dimensions/wiring remain E02 release scope</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>CURRENT_CONTROL_CHECKS.json; unchanged reservations mutually clear</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>DIGITAL PASS / NO BUILD RELEASE</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>CURRENT_CONTROL_CHECKS.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="38" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Mechanical digital preparation</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>CLOSED CALCULATION ONLY</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Filter tolerance window and cabinet joint-demand tools</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>M01/M02/M03 physical and material inputs remain OPEN</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>MECHANICAL_REQUIREMENTS.json;10 synthetic tests</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>TOOL PASS / NO SEAL OR STRUCTURAL RELEASE</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>../../mechanical_package/batch_closure/MECHANICAL_REQUIREMENTS.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="38" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>D07</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Electrical digital preparation</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>CLOSED CALCULATION ONLY</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Source/fan path voltage fault and hazard screens</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>E01/E02 real component/coordination inputs remain OPEN</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>ELECTRICAL_BATCH_SCREEN.json;8 synthetic tests</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>TOOL PASS / NO PROTECTION RELEASE</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>../batch_closure/ELECTRICAL_BATCH_SCREEN.json</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J16"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16853,7 +19134,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17411,540 +19692,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="35.1" customWidth="1" min="3" max="3"/>
-    <col width="17.55" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="24.05" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Quantity_basis</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Evidence_status</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Unresolved</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="38" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>F1-F4</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>ARCTIC P14 Max ACFAN00287A</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Exact OEM reference</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Delivered revision and cable details; guard and duty integration</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Electrical BOM; OEM sources S1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="53" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>FL1-FL2</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>IKEA STARKVIND104.633.30 particle filter</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Experimental reference only</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>370x290x40 catalogue envelope; pressure curve/frame/seal tolerances unknown; OEM specifies STARKVIND use only</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>r02_adapter/README.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>PS1</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Noctua NV-PS1 with NA-AC10</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Exact OEM reference</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>12V2A24W; startup/auxiliary/site suitability not closed</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Electrical BOM S2/S6</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>SC1</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Noctua NA-FC1</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Exact OEM reference</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Speed controller is not protective isolation</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Electrical BOM S3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Noctua NA-FH1 with NA-EC1</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Exact OEM reference</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>24W selected input; self-reset; only port1 RPM upstream; SATA unused</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Electrical BOM S4/S5</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>EXT</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>2 candidate leads</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>NA-EC1 300mm from NA-SEC1 kit</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Candidate not selected</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Kit contains3 leads; dimensions pending; check total connection count before purchase</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Harness README</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CAB</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>1 assembly</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>R03M panels and cleats</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Custom proposed geometry</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Grade/joints/strength/finish unreleased; panel inventory is controlling geometry</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>CAD_PART_INVENTORY.csv and15 DXFs</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="38" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>GUARD</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>2 assemblies</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>R03M welded perforated guards</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Custom proposed geometry</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Strength/reach/weld criteria unreleased;1mm not approved</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>GUARD_BLANKS.csv; guard_pattern.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="38" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>FIX</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>1 scheduled set</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>R03M fasteners and compression limiters</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Proposed geometry</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Use FASTENER_SCHEDULE; do not add inventory quantities again; grade/torque unresolved</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>FASTENER_SCHEDULE.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="38" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>SEAL</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>1 design set</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Filter/fan/penetration seals</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Unselected material</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Gasket dimensions are installed envelopes, not a compression specification</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>CAD inventory; mechanical_screen.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>FEET</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Retained feet</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Proposed geometry</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Material/bearing/stability not released</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Mechanical package</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="38" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>PR1</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>1 assembly</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Protection and service isolation</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>UNSELECTED</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Not replaced by hub fuse, PWM or software model</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Electrical interfaces J09/J11</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>1 assembly</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Controls enclosure and cable restraints</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>UNSELECTED</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>140x100x40 reservation is not selected enclosure or complete fit</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Electrical package</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>TEST</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>1 service scope</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated airflow/pressure/power/noise/PM measurement</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>UNSELECTED</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Rent or commission test service; no college lab assumed</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Validation package</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="38" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>BUILD</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>1 service scope</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Fabrication assembly and qualified review</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>UNSELECTED</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Internal engineers review; outsource workshop work as needed</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Review register</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F16"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>